--- a/artfynd/A 26639-2026 artfynd.xlsx
+++ b/artfynd/A 26639-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>91835084</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720128.1240118507</v>
+        <v>720128</v>
       </c>
       <c r="R2" t="n">
-        <v>7334902.888800913</v>
+        <v>7334903</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-10-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-10-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,6 +769,112 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>134434127</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93283</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>720229</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7334876</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26639-2026 artfynd.xlsx
+++ b/artfynd/A 26639-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91835084</v>
+        <v>135410049</v>
       </c>
       <c r="B2" t="n">
-        <v>93197</v>
+        <v>79451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>863</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypogymnia austerodes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Räsänen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Telebäcken-Tvättstugubäcken, Lu lm</t>
+          <t>tellejåkk juli 2026, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720128</v>
+        <v>720236</v>
       </c>
       <c r="R2" t="n">
-        <v>7334903</v>
+        <v>7334843</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,64 +770,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134434127</v>
+        <v>135403993</v>
       </c>
       <c r="B3" t="n">
-        <v>93283</v>
+        <v>92188</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>3008</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720229</v>
+        <v>720181</v>
       </c>
       <c r="R3" t="n">
-        <v>7334876</v>
+        <v>7334837</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -841,17 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -866,15 +877,3102 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135404002</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91896</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>720224</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7334854</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>91835084</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Telebäcken-Tvättstugubäcken, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>720128</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7334903</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-10-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-10-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135402500</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>720090</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7334839</v>
+      </c>
+      <c r="S6" t="n">
+        <v>14</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135402502</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>720172</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7334806</v>
+      </c>
+      <c r="S7" t="n">
+        <v>8</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135402503</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>720212</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7334860</v>
+      </c>
+      <c r="S8" t="n">
+        <v>7</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135403867</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>720236</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7334841</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135403990</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>720136</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7334843</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135403996</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>720211</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7334859</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135404000</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>720193</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7334868</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135404001</v>
+      </c>
+      <c r="B13" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>720214</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7334845</v>
+      </c>
+      <c r="S13" t="n">
+        <v>12</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135404417</v>
+      </c>
+      <c r="B14" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>720195</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7334851</v>
+      </c>
+      <c r="S14" t="n">
+        <v>7</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135404418</v>
+      </c>
+      <c r="B15" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>720208</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7334912</v>
+      </c>
+      <c r="S15" t="n">
+        <v>12</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135408002</v>
+      </c>
+      <c r="B16" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Tellejock, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>720137</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7334872</v>
+      </c>
+      <c r="S16" t="n">
+        <v>7</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135408003</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Tellejock, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>720181</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7334871</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135410051</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93271</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>tellejåkk juli 2026, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>720186</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7334829</v>
+      </c>
+      <c r="S18" t="n">
+        <v>13</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135410045</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93275</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>tellejåkk juli 2026, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>720191</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7334923</v>
+      </c>
+      <c r="S19" t="n">
+        <v>11</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134434127</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93283</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>720229</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7334876</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX20" t="inlineStr">
         <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135403995</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78776</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>720190</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7334890</v>
+      </c>
+      <c r="S21" t="n">
+        <v>9</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135403866</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>720202</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7334913</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135403991</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>720134</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7334845</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135403994</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>720191</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7334871</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135408005</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Tellejock, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>720212</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7334885</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135410050</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>tellejåkk juli 2026, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>720236</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7334843</v>
+      </c>
+      <c r="S26" t="n">
+        <v>8</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135403666</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58079</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>720143</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7334844</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135404003</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>720213</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7334858</v>
+      </c>
+      <c r="S28" t="n">
+        <v>6</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135408004</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Tellejock, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>720220</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7334868</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135408006</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Tellejock, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>720217</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7334878</v>
+      </c>
+      <c r="S30" t="n">
+        <v>9</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135408142</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>720182</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7334898</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135410046</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80267</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>266179</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lecidea subhumida</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Vain.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>tellejåkk juli 2026, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>720205</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7334872</v>
+      </c>
+      <c r="S32" t="n">
+        <v>12</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26639-2026 artfynd.xlsx
+++ b/artfynd/A 26639-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135410049</v>
+        <v>135403993</v>
       </c>
       <c r="B2" t="n">
-        <v>79451</v>
+        <v>92188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>863</v>
+        <v>3008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk blåslav</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypogymnia austerodes</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Räsänen</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>tellejåkk juli 2026, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720236</v>
+        <v>720181</v>
       </c>
       <c r="R2" t="n">
-        <v>7334843</v>
+        <v>7334837</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,44 +770,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135403993</v>
+        <v>135404002</v>
       </c>
       <c r="B3" t="n">
-        <v>92188</v>
+        <v>91896</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3008</v>
+        <v>3242</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Timmerticka</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Amyloporia sinuosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Rajchenb. &amp; al.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720181</v>
+        <v>720224</v>
       </c>
       <c r="R3" t="n">
-        <v>7334837</v>
+        <v>7334854</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135404002</v>
+        <v>91835084</v>
       </c>
       <c r="B4" t="n">
-        <v>91896</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,37 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3242</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tellejokk, Lu lm</t>
+          <t>Telebäcken-Tvättstugubäcken, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720224</v>
+        <v>720128</v>
       </c>
       <c r="R4" t="n">
-        <v>7334854</v>
+        <v>7334903</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,22 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2020-10-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91835084</v>
+        <v>135402500</v>
       </c>
       <c r="B5" t="n">
-        <v>93197</v>
+        <v>93271</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,17 +1017,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Telebäcken-Tvättstugubäcken, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720128</v>
+        <v>720090</v>
       </c>
       <c r="R5" t="n">
-        <v>7334903</v>
+        <v>7334839</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1061,12 +1051,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,7 +1081,7 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -1093,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135402500</v>
+        <v>135402502</v>
       </c>
       <c r="B6" t="n">
         <v>93271</v>
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720090</v>
+        <v>720172</v>
       </c>
       <c r="R6" t="n">
-        <v>7334839</v>
+        <v>7334806</v>
       </c>
       <c r="S6" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135402502</v>
+        <v>135402503</v>
       </c>
       <c r="B7" t="n">
         <v>93271</v>
@@ -1235,13 +1235,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720172</v>
+        <v>720212</v>
       </c>
       <c r="R7" t="n">
-        <v>7334806</v>
+        <v>7334860</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135402503</v>
+        <v>135403867</v>
       </c>
       <c r="B8" t="n">
         <v>93271</v>
@@ -1342,13 +1342,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720212</v>
+        <v>720236</v>
       </c>
       <c r="R8" t="n">
-        <v>7334860</v>
+        <v>7334841</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1402,19 +1402,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135403867</v>
+        <v>135403990</v>
       </c>
       <c r="B9" t="n">
         <v>93271</v>
@@ -1445,14 +1445,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720236</v>
+        <v>720136</v>
       </c>
       <c r="R9" t="n">
-        <v>7334841</v>
+        <v>7334843</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1509,19 +1509,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135403990</v>
+        <v>135403996</v>
       </c>
       <c r="B10" t="n">
         <v>93271</v>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>720136</v>
+        <v>720211</v>
       </c>
       <c r="R10" t="n">
-        <v>7334843</v>
+        <v>7334859</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,7 +1628,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135403996</v>
+        <v>135404000</v>
       </c>
       <c r="B11" t="n">
         <v>93271</v>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>720211</v>
+        <v>720193</v>
       </c>
       <c r="R11" t="n">
-        <v>7334859</v>
+        <v>7334868</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,7 +1735,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135404000</v>
+        <v>135404001</v>
       </c>
       <c r="B12" t="n">
         <v>93271</v>
@@ -1770,13 +1770,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720193</v>
+        <v>720214</v>
       </c>
       <c r="R12" t="n">
-        <v>7334868</v>
+        <v>7334845</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135404001</v>
+        <v>135404417</v>
       </c>
       <c r="B13" t="n">
         <v>93271</v>
@@ -1877,13 +1877,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720214</v>
+        <v>720195</v>
       </c>
       <c r="R13" t="n">
-        <v>7334845</v>
+        <v>7334851</v>
       </c>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1937,19 +1937,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135404417</v>
+        <v>135404418</v>
       </c>
       <c r="B14" t="n">
         <v>93271</v>
@@ -1984,13 +1984,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720195</v>
+        <v>720208</v>
       </c>
       <c r="R14" t="n">
-        <v>7334851</v>
+        <v>7334912</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,7 +2056,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135404418</v>
+        <v>135408002</v>
       </c>
       <c r="B15" t="n">
         <v>93271</v>
@@ -2087,17 +2087,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tellejokk, Lu lm</t>
+          <t>Tellejock, Lu lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720208</v>
+        <v>720137</v>
       </c>
       <c r="R15" t="n">
-        <v>7334912</v>
+        <v>7334872</v>
       </c>
       <c r="S15" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2151,19 +2151,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135408002</v>
+        <v>135408003</v>
       </c>
       <c r="B16" t="n">
         <v>93271</v>
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>720137</v>
+        <v>720181</v>
       </c>
       <c r="R16" t="n">
-        <v>7334872</v>
+        <v>7334871</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,7 +2270,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135408003</v>
+        <v>135410051</v>
       </c>
       <c r="B17" t="n">
         <v>93271</v>
@@ -2301,17 +2301,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Tellejock, Lu lm</t>
+          <t>tellejåkk juli 2026, Lu lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>720181</v>
+        <v>720186</v>
       </c>
       <c r="R17" t="n">
-        <v>7334871</v>
+        <v>7334829</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2365,60 +2365,63 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135410051</v>
+        <v>135410045</v>
       </c>
       <c r="B18" t="n">
-        <v>93271</v>
+        <v>93275</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>tellejåkk juli 2026, Lu lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>720186</v>
+        <v>720191</v>
       </c>
       <c r="R18" t="n">
-        <v>7334829</v>
+        <v>7334923</v>
       </c>
       <c r="S18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2447,7 +2450,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2457,7 +2460,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2466,6 +2469,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2477,55 +2481,59 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>per-erik mukka, Christina Boyd</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135410045</v>
+        <v>134434127</v>
       </c>
       <c r="B19" t="n">
-        <v>93275</v>
+        <v>93283</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4365</v>
+        <v>4366</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>tellejåkk juli 2026, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>720191</v>
+        <v>720229</v>
       </c>
       <c r="R19" t="n">
-        <v>7334923</v>
+        <v>7334876</v>
       </c>
       <c r="S19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2549,22 +2557,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2579,22 +2582,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134434127</v>
+        <v>135403995</v>
       </c>
       <c r="B20" t="n">
-        <v>93283</v>
+        <v>78776</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2602,41 +2605,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4366</v>
+        <v>6437</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>720229</v>
+        <v>720190</v>
       </c>
       <c r="R20" t="n">
-        <v>7334876</v>
+        <v>7334890</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2660,17 +2659,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2685,22 +2689,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135403995</v>
+        <v>135403866</v>
       </c>
       <c r="B21" t="n">
-        <v>78776</v>
+        <v>79992</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2708,37 +2712,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Tellejokk, Lu lm</t>
+          <t>Tellejåkk, Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>720190</v>
+        <v>720202</v>
       </c>
       <c r="R21" t="n">
-        <v>7334890</v>
+        <v>7334913</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2767,7 +2771,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2777,7 +2781,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2792,19 +2796,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135403866</v>
+        <v>135403991</v>
       </c>
       <c r="B22" t="n">
         <v>79992</v>
@@ -2835,14 +2839,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>720202</v>
+        <v>720134</v>
       </c>
       <c r="R22" t="n">
-        <v>7334913</v>
+        <v>7334845</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2874,7 +2878,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2884,7 +2888,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2899,19 +2903,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135403991</v>
+        <v>135403994</v>
       </c>
       <c r="B23" t="n">
         <v>79992</v>
@@ -2946,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>720134</v>
+        <v>720191</v>
       </c>
       <c r="R23" t="n">
-        <v>7334845</v>
+        <v>7334871</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2981,7 +2985,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2991,7 +2995,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3018,7 +3022,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135403994</v>
+        <v>135408005</v>
       </c>
       <c r="B24" t="n">
         <v>79992</v>
@@ -3049,14 +3053,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Tellejokk, Lu lm</t>
+          <t>Tellejock, Lu lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>720191</v>
+        <v>720212</v>
       </c>
       <c r="R24" t="n">
-        <v>7334871</v>
+        <v>7334885</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3088,7 +3092,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3098,7 +3102,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3113,19 +3117,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135408005</v>
+        <v>135410050</v>
       </c>
       <c r="B25" t="n">
         <v>79992</v>
@@ -3156,17 +3160,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Tellejock, Lu lm</t>
+          <t>tellejåkk juli 2026, Lu lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>720212</v>
+        <v>720236</v>
       </c>
       <c r="R25" t="n">
-        <v>7334885</v>
+        <v>7334843</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3195,7 +3199,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3205,7 +3209,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3220,22 +3224,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135410050</v>
+        <v>135403666</v>
       </c>
       <c r="B26" t="n">
-        <v>79992</v>
+        <v>58079</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3243,37 +3247,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>103031</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>tellejåkk juli 2026, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>720236</v>
+        <v>720143</v>
       </c>
       <c r="R26" t="n">
-        <v>7334843</v>
+        <v>7334844</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3302,7 +3306,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3312,7 +3316,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3327,22 +3331,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135403666</v>
+        <v>135404003</v>
       </c>
       <c r="B27" t="n">
-        <v>58079</v>
+        <v>79396</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3350,21 +3354,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103031</v>
+        <v>260591</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3374,13 +3378,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>720143</v>
+        <v>720213</v>
       </c>
       <c r="R27" t="n">
-        <v>7334844</v>
+        <v>7334858</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3409,7 +3413,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3419,7 +3423,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3434,19 +3438,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135404003</v>
+        <v>135408004</v>
       </c>
       <c r="B28" t="n">
         <v>79396</v>
@@ -3477,17 +3481,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Tellejokk, Lu lm</t>
+          <t>Tellejock, Lu lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>720213</v>
+        <v>720220</v>
       </c>
       <c r="R28" t="n">
-        <v>7334858</v>
+        <v>7334868</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3516,7 +3520,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3526,7 +3530,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3541,19 +3545,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135408004</v>
+        <v>135408006</v>
       </c>
       <c r="B29" t="n">
         <v>79396</v>
@@ -3588,13 +3592,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>720220</v>
+        <v>720217</v>
       </c>
       <c r="R29" t="n">
-        <v>7334868</v>
+        <v>7334878</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3623,7 +3627,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3633,7 +3637,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3660,7 +3664,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135408006</v>
+        <v>135408142</v>
       </c>
       <c r="B30" t="n">
         <v>79396</v>
@@ -3691,17 +3695,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tellejock, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>720217</v>
+        <v>720182</v>
       </c>
       <c r="R30" t="n">
-        <v>7334878</v>
+        <v>7334898</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3730,7 +3734,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3740,7 +3744,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3755,60 +3759,58 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135408142</v>
+        <v>135410046</v>
       </c>
       <c r="B31" t="n">
-        <v>79396</v>
+        <v>80267</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
+        <v>266179</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Lecidea subhumida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Vain.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tellejokk, Lu lm</t>
+          <t>tellejåkk juli 2026, Lu lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>720182</v>
+        <v>720205</v>
       </c>
       <c r="R31" t="n">
-        <v>7334898</v>
+        <v>7334872</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3837,7 +3839,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3847,7 +3849,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3856,123 +3858,22 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>per-erik mukka, Christina Boyd</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>135410046</v>
-      </c>
-      <c r="B32" t="n">
-        <v>80267</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>266179</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Lecidea subhumida</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Vain.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>tellejåkk juli 2026, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>720205</v>
-      </c>
-      <c r="R32" t="n">
-        <v>7334872</v>
-      </c>
-      <c r="S32" t="n">
-        <v>12</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Jokkmokk</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Jokkmokk</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2026-07-25</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26639-2026 artfynd.xlsx
+++ b/artfynd/A 26639-2026 artfynd.xlsx
@@ -3664,7 +3664,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135408142</v>
+        <v>135504169</v>
       </c>
       <c r="B30" t="n">
         <v>79396</v>

--- a/artfynd/A 26639-2026 artfynd.xlsx
+++ b/artfynd/A 26639-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403993</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835084</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1090,6 +1110,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402500</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402502</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402503</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403867</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1518,6 +1558,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403990</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1625,6 +1670,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403996</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1732,6 +1782,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404000</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1839,6 +1894,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404001</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1946,6 +2006,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404417</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2053,6 +2118,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404418</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2160,6 +2230,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408002</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2267,6 +2342,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408003</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2374,6 +2454,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135410051</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2485,6 +2570,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135410045</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2591,6 +2681,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134434127</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2698,6 +2793,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403995</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2805,6 +2905,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403866</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2912,6 +3017,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403991</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3019,6 +3129,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403994</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3126,6 +3241,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408005</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3233,6 +3353,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135410050</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3340,6 +3465,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403666</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3447,6 +3577,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404003</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3554,6 +3689,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408004</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3661,6 +3801,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408006</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3768,6 +3913,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504169</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3874,8 +4024,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135410046</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 26639-2026 artfynd.xlsx
+++ b/artfynd/A 26639-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135403993</v>
       </c>
       <c r="B2" t="n">
-        <v>92188</v>
+        <v>92230</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135404002</v>
       </c>
       <c r="B3" t="n">
-        <v>91896</v>
+        <v>91938</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135402500</v>
       </c>
       <c r="B5" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135402502</v>
       </c>
       <c r="B6" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135402503</v>
       </c>
       <c r="B7" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>135403867</v>
       </c>
       <c r="B8" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>135403990</v>
       </c>
       <c r="B9" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>135403996</v>
       </c>
       <c r="B10" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>135404000</v>
       </c>
       <c r="B11" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>135404001</v>
       </c>
       <c r="B12" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>135404417</v>
       </c>
       <c r="B13" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>135404418</v>
       </c>
       <c r="B14" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>135408002</v>
       </c>
       <c r="B15" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>135408003</v>
       </c>
       <c r="B16" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>135410051</v>
       </c>
       <c r="B17" t="n">
-        <v>93271</v>
+        <v>93313</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>135410045</v>
       </c>
       <c r="B18" t="n">
-        <v>93275</v>
+        <v>93317</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>135403995</v>
       </c>
       <c r="B20" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>135403866</v>
       </c>
       <c r="B21" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>135403991</v>
       </c>
       <c r="B22" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>135403994</v>
       </c>
       <c r="B23" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>135408005</v>
       </c>
       <c r="B24" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>135410050</v>
       </c>
       <c r="B25" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>135403666</v>
       </c>
       <c r="B26" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>135404003</v>
       </c>
       <c r="B27" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>135408004</v>
       </c>
       <c r="B28" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>135408006</v>
       </c>
       <c r="B29" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>135504169</v>
       </c>
       <c r="B30" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>135410046</v>
       </c>
       <c r="B31" t="n">
-        <v>80267</v>
+        <v>80305</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 26639-2026 artfynd.xlsx
+++ b/artfynd/A 26639-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135403993</v>
       </c>
       <c r="B2" t="n">
-        <v>92230</v>
+        <v>92257</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135404002</v>
       </c>
       <c r="B3" t="n">
-        <v>91938</v>
+        <v>91965</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135402500</v>
       </c>
       <c r="B5" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135402502</v>
       </c>
       <c r="B6" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135402503</v>
       </c>
       <c r="B7" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>135403867</v>
       </c>
       <c r="B8" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>135403990</v>
       </c>
       <c r="B9" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>135403996</v>
       </c>
       <c r="B10" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>135404000</v>
       </c>
       <c r="B11" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>135404001</v>
       </c>
       <c r="B12" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>135404417</v>
       </c>
       <c r="B13" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>135404418</v>
       </c>
       <c r="B14" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>135408002</v>
       </c>
       <c r="B15" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>135408003</v>
       </c>
       <c r="B16" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>135410051</v>
       </c>
       <c r="B17" t="n">
-        <v>93313</v>
+        <v>93340</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>135410045</v>
       </c>
       <c r="B18" t="n">
-        <v>93317</v>
+        <v>93344</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>135403995</v>
       </c>
       <c r="B20" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>135403866</v>
       </c>
       <c r="B21" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>135403991</v>
       </c>
       <c r="B22" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>135403994</v>
       </c>
       <c r="B23" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>135408005</v>
       </c>
       <c r="B24" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>135410050</v>
       </c>
       <c r="B25" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>135404003</v>
       </c>
       <c r="B27" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>135408004</v>
       </c>
       <c r="B28" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>135408006</v>
       </c>
       <c r="B29" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>135504169</v>
       </c>
       <c r="B30" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>135410046</v>
       </c>
       <c r="B31" t="n">
-        <v>80305</v>
+        <v>80332</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 26639-2026 artfynd.xlsx
+++ b/artfynd/A 26639-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91835084</v>
+        <v>135403993</v>
       </c>
       <c r="B2" t="n">
-        <v>93197</v>
+        <v>92262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>3008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Telebäcken-Tvättstugubäcken, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720128</v>
+        <v>720181</v>
       </c>
       <c r="R2" t="n">
-        <v>7334903</v>
+        <v>7334837</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-10-15</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +775,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91835084</t>
+          <t>https://artportalen.se/Sighting/135403993</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134434127</v>
+        <v>135404002</v>
       </c>
       <c r="B3" t="n">
-        <v>93283</v>
+        <v>91970</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,41 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>3242</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tellejåkk, Lu lm</t>
+          <t>Tellejokk, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720229</v>
+        <v>720224</v>
       </c>
       <c r="R3" t="n">
-        <v>7334876</v>
+        <v>7334854</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,17 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,18 +887,3146 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Christina Boyd, per-erik mukka</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135404002</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>91835084</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Telebäcken-Tvättstugubäcken, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>720128</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7334903</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-10-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-10-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91835084</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135402500</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>720090</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7334839</v>
+      </c>
+      <c r="S5" t="n">
+        <v>14</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402500</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135402502</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>720172</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7334806</v>
+      </c>
+      <c r="S6" t="n">
+        <v>8</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402502</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135402503</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>720212</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7334860</v>
+      </c>
+      <c r="S7" t="n">
+        <v>7</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135402503</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135403867</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>720236</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7334841</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403867</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135403990</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>720136</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7334843</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403990</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135403996</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>720211</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7334859</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403996</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135404000</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>720193</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7334868</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404000</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135404001</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>720214</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7334845</v>
+      </c>
+      <c r="S12" t="n">
+        <v>12</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404001</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135404417</v>
+      </c>
+      <c r="B13" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>720195</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7334851</v>
+      </c>
+      <c r="S13" t="n">
+        <v>7</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404417</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135404418</v>
+      </c>
+      <c r="B14" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>720208</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7334912</v>
+      </c>
+      <c r="S14" t="n">
+        <v>12</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404418</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135408002</v>
+      </c>
+      <c r="B15" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tellejock, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>720137</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7334872</v>
+      </c>
+      <c r="S15" t="n">
+        <v>7</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408002</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135408003</v>
+      </c>
+      <c r="B16" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Tellejock, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>720181</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7334871</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408003</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135410051</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93345</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>tellejåkk juli 2026, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>720186</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7334829</v>
+      </c>
+      <c r="S17" t="n">
+        <v>13</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135410051</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135410045</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93349</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>tellejåkk juli 2026, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>720191</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7334923</v>
+      </c>
+      <c r="S18" t="n">
+        <v>11</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135410045</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134434127</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93283</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>720229</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7334876</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/134434127</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135403995</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78844</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>720190</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7334890</v>
+      </c>
+      <c r="S20" t="n">
+        <v>9</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403995</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135403866</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Tellejåkk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>720202</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7334913</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403866</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135403991</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>720134</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7334845</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403991</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135403994</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>720191</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7334871</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403994</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135408005</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Tellejock, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>720212</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7334885</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408005</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135410050</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>tellejåkk juli 2026, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>720236</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7334843</v>
+      </c>
+      <c r="S25" t="n">
+        <v>8</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135410050</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135403666</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58084</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>720143</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7334844</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135403666</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135404003</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>720213</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7334858</v>
+      </c>
+      <c r="S27" t="n">
+        <v>6</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135404003</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135408004</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Tellejock, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>720220</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7334868</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408004</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135408006</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Tellejock, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>720217</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7334878</v>
+      </c>
+      <c r="S29" t="n">
+        <v>9</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135408006</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135504169</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Tellejokk, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>720182</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7334898</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135504169</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135410046</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80335</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>266179</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lecidea subhumida</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Vain.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>tellejåkk juli 2026, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>720205</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7334872</v>
+      </c>
+      <c r="S31" t="n">
+        <v>12</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>per-erik mukka, Christina Boyd</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135410046</t>
         </is>
       </c>
     </row>
@@ -895,6 +4034,34 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26639-2026 artfynd.xlsx
+++ b/artfynd/A 26639-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135403993</v>
       </c>
       <c r="B2" t="n">
-        <v>92262</v>
+        <v>92264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135404002</v>
       </c>
       <c r="B3" t="n">
-        <v>91970</v>
+        <v>91972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135402500</v>
       </c>
       <c r="B5" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135402502</v>
       </c>
       <c r="B6" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135402503</v>
       </c>
       <c r="B7" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>135403867</v>
       </c>
       <c r="B8" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>135403990</v>
       </c>
       <c r="B9" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>135403996</v>
       </c>
       <c r="B10" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>135404000</v>
       </c>
       <c r="B11" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>135404001</v>
       </c>
       <c r="B12" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>135404417</v>
       </c>
       <c r="B13" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>135404418</v>
       </c>
       <c r="B14" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>135408002</v>
       </c>
       <c r="B15" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>135408003</v>
       </c>
       <c r="B16" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>135410051</v>
       </c>
       <c r="B17" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>135410045</v>
       </c>
       <c r="B18" t="n">
-        <v>93349</v>
+        <v>93351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 26639-2026 artfynd.xlsx
+++ b/artfynd/A 26639-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135403993</v>
       </c>
       <c r="B2" t="n">
-        <v>92264</v>
+        <v>92278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135404002</v>
       </c>
       <c r="B3" t="n">
-        <v>91972</v>
+        <v>91986</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135402500</v>
       </c>
       <c r="B5" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135402502</v>
       </c>
       <c r="B6" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135402503</v>
       </c>
       <c r="B7" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>135403867</v>
       </c>
       <c r="B8" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>135403990</v>
       </c>
       <c r="B9" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>135403996</v>
       </c>
       <c r="B10" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>135404000</v>
       </c>
       <c r="B11" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,7 +1793,7 @@
         <v>135404001</v>
       </c>
       <c r="B12" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>135404417</v>
       </c>
       <c r="B13" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>135404418</v>
       </c>
       <c r="B14" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>135408002</v>
       </c>
       <c r="B15" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>135408003</v>
       </c>
       <c r="B16" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>135410051</v>
       </c>
       <c r="B17" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>135410045</v>
       </c>
       <c r="B18" t="n">
-        <v>93351</v>
+        <v>93366</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2692,7 +2692,7 @@
         <v>135403995</v>
       </c>
       <c r="B20" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>135403866</v>
       </c>
       <c r="B21" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>135403991</v>
       </c>
       <c r="B22" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>135403994</v>
       </c>
       <c r="B23" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3140,7 +3140,7 @@
         <v>135408005</v>
       </c>
       <c r="B24" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>135410050</v>
       </c>
       <c r="B25" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>135403666</v>
       </c>
       <c r="B26" t="n">
-        <v>58084</v>
+        <v>58086</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>135404003</v>
       </c>
       <c r="B27" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>135408004</v>
       </c>
       <c r="B28" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>135408006</v>
       </c>
       <c r="B29" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3812,7 +3812,7 @@
         <v>135504169</v>
       </c>
       <c r="B30" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
         <v>135410046</v>
       </c>
       <c r="B31" t="n">
-        <v>80335</v>
+        <v>80337</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 26639-2026 artfynd.xlsx
+++ b/artfynd/A 26639-2026 artfynd.xlsx
@@ -3812,7 +3812,7 @@
         <v>135504169</v>
       </c>
       <c r="B30" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
